--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N58_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N58_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>71.54176250425284</v>
+        <v>11.62553640694109</v>
       </c>
       <c r="D2" t="n">
-        <v>71.8293192731233</v>
+        <v>11.67226438188254</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
